--- a/Output/gls_model_interruption1_weekly_output.xlsx
+++ b/Output/gls_model_interruption1_weekly_output.xlsx
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
